--- a/AtchisonRegime/Outputs/Japan/MSCI_Europe/df_regEquityReturns_MSCI_Europe.xlsx
+++ b/AtchisonRegime/Outputs/Japan/MSCI_Europe/df_regEquityReturns_MSCI_Europe.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q316"/>
+  <dimension ref="A1:Q317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17857,7 +17857,7 @@
         <v>0.2744934912130399</v>
       </c>
       <c r="C306" t="n">
-        <v>0.1143020237392588</v>
+        <v>0.09483981685732353</v>
       </c>
       <c r="D306" t="b">
         <v>1</v>
@@ -17914,7 +17914,7 @@
         <v>0.247043822107174</v>
       </c>
       <c r="C307" t="n">
-        <v>0.07839956235737192</v>
+        <v>0.02622896941243575</v>
       </c>
       <c r="D307" t="b">
         <v>1</v>
@@ -17971,7 +17971,7 @@
         <v>0.2764810102827051</v>
       </c>
       <c r="C308" t="n">
-        <v>-0.04075924110783925</v>
+        <v>-0.08493118817654892</v>
       </c>
       <c r="D308" t="b">
         <v>1</v>
@@ -18028,7 +18028,7 @@
         <v>0.2775195757319146</v>
       </c>
       <c r="C309" t="n">
-        <v>-0.1700193597796587</v>
+        <v>-0.1830661174124763</v>
       </c>
       <c r="D309" t="b">
         <v>1</v>
@@ -18085,7 +18085,7 @@
         <v>0.1358080368870456</v>
       </c>
       <c r="C310" t="n">
-        <v>-0.2210773005275436</v>
+        <v>-0.2048588663815025</v>
       </c>
       <c r="D310" t="b">
         <v>1</v>
@@ -18142,7 +18142,7 @@
         <v>-0.1011804355610571</v>
       </c>
       <c r="C311" t="n">
-        <v>-0.3207525013009814</v>
+        <v>-0.2269911939414751</v>
       </c>
       <c r="D311" t="b">
         <v>1</v>
@@ -18199,7 +18199,7 @@
         <v>-0.2269313581600936</v>
       </c>
       <c r="C312" t="n">
-        <v>-0.2836938197787018</v>
+        <v>-0.2150979956911355</v>
       </c>
       <c r="D312" t="b">
         <v>1</v>
@@ -18256,7 +18256,7 @@
         <v>0.1293460533979883</v>
       </c>
       <c r="C313" t="n">
-        <v>-0.2927346215005262</v>
+        <v>-0.150710709240619</v>
       </c>
       <c r="D313" t="b">
         <v>1</v>
@@ -18313,7 +18313,7 @@
         <v>0.8294513901668797</v>
       </c>
       <c r="C314" t="n">
-        <v>-0.2023349038685079</v>
+        <v>-0.08552533138729648</v>
       </c>
       <c r="D314" t="b">
         <v>1</v>
@@ -18370,7 +18370,7 @@
         <v>1.256555449945676</v>
       </c>
       <c r="C315" t="n">
-        <v>-0.1575668569988701</v>
+        <v>-0.07846608629638509</v>
       </c>
       <c r="D315" t="b">
         <v>1</v>
@@ -18424,10 +18424,10 @@
         <v>45747</v>
       </c>
       <c r="B316" t="n">
-        <v>1.366111373837551</v>
+        <v>1.316054207954405</v>
       </c>
       <c r="C316" t="n">
-        <v>-0.1091321474455471</v>
+        <v>-0.1099834431928019</v>
       </c>
       <c r="D316" t="b">
         <v>1</v>
@@ -18473,6 +18473,63 @@
         <v>121.9706019973393</v>
       </c>
       <c r="Q316" t="n">
+        <v>156.8896828234528</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B317" t="n">
+        <v>1.008852221221361</v>
+      </c>
+      <c r="C317" t="n">
+        <v>0.04018897446938442</v>
+      </c>
+      <c r="D317" t="b">
+        <v>1</v>
+      </c>
+      <c r="E317" t="b">
+        <v>0</v>
+      </c>
+      <c r="F317" t="n">
+        <v>1.83191753619591</v>
+      </c>
+      <c r="G317" t="n">
+        <v>325618.0893537902</v>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>Type 4: Weakening CLI &amp; Rising Inflation</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>Type 4</t>
+        </is>
+      </c>
+      <c r="J317" t="n">
+        <v>0</v>
+      </c>
+      <c r="K317" t="n">
+        <v>0</v>
+      </c>
+      <c r="L317" t="n">
+        <v>1.83191753619591</v>
+      </c>
+      <c r="M317" t="n">
+        <v>0</v>
+      </c>
+      <c r="N317" t="n">
+        <v>213.9037554384482</v>
+      </c>
+      <c r="O317" t="n">
+        <v>80.50683709756157</v>
+      </c>
+      <c r="P317" t="n">
+        <v>124.2050028443323</v>
+      </c>
+      <c r="Q317" t="n">
         <v>156.8896828234528</v>
       </c>
     </row>
